--- a/data/test3/testXlsx3.xlsx
+++ b/data/test3/testXlsx3.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="13380"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,9 +29,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
-  <si>
-    <t>字段名称</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="27">
+  <si>
+    <t>##字段名称</t>
   </si>
   <si>
     <t>id</t>
@@ -46,10 +46,13 @@
     <t>skill_pool</t>
   </si>
   <si>
-    <t>test</t>
-  </si>
-  <si>
-    <t>数据类型</t>
+    <t>*item_cost</t>
+  </si>
+  <si>
+    <t>*item_award</t>
+  </si>
+  <si>
+    <t>##数据类型</t>
   </si>
   <si>
     <t>int</t>
@@ -61,7 +64,22 @@
     <t>(list#sep=|),WeaponType</t>
   </si>
   <si>
-    <t>字段备注</t>
+    <t>Items.ItemCost</t>
+  </si>
+  <si>
+    <t>(list#sep=|),Items.ItemAward</t>
+  </si>
+  <si>
+    <t>(list#sep=|),Items.ItemTest</t>
+  </si>
+  <si>
+    <t>##类型注释</t>
+  </si>
+  <si>
+    <t>num</t>
+  </si>
+  <si>
+    <t>##字段备注</t>
   </si>
   <si>
     <t>武器名称</t>
@@ -73,7 +91,13 @@
     <t>技能池列表</t>
   </si>
   <si>
-    <t>测试</t>
+    <t>道具id</t>
+  </si>
+  <si>
+    <t>道具数量</t>
+  </si>
+  <si>
+    <t>测试id</t>
   </si>
   <si>
     <t>单手剑</t>
@@ -82,16 +106,10 @@
     <t>Sword|Dagger</t>
   </si>
   <si>
-    <t>测试配置1</t>
-  </si>
-  <si>
     <t>仪式匕首</t>
   </si>
   <si>
     <t>Dagger</t>
-  </si>
-  <si>
-    <t>测试配置2</t>
   </si>
 </sst>
 </file>
@@ -463,7 +481,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -478,6 +496,43 @@
       <right style="thin">
         <color auto="1"/>
       </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color auto="1"/>
       </top>
@@ -610,7 +665,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
@@ -622,34 +677,34 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="8" borderId="0">
@@ -734,7 +789,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -743,6 +798,27 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1058,16 +1134,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="5"/>
+  <dimension ref="A1:L16"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="15.1111111111111" customWidth="1"/>
-    <col min="3" max="3" width="13.8888888888889" customWidth="1"/>
+    <col min="1" max="1" width="15.1083333333333" customWidth="1"/>
+    <col min="3" max="3" width="13.8916666666667" customWidth="1"/>
     <col min="4" max="4" width="27.6666666666667" customWidth="1"/>
-    <col min="5" max="5" width="19.7777777777778" customWidth="1"/>
+    <col min="5" max="5" width="19.775" customWidth="1"/>
+    <col min="6" max="6" width="12.625" customWidth="1"/>
+    <col min="7" max="7" width="13.875" customWidth="1"/>
+    <col min="8" max="8" width="14.5" customWidth="1"/>
+    <col min="9" max="9" width="20.75" customWidth="1"/>
+    <col min="10" max="10" width="13.5" customWidth="1"/>
+    <col min="11" max="11" width="14.125" customWidth="1"/>
+    <col min="12" max="12" width="17.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:6">
+    <row r="1" s="1" customFormat="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1083,85 +1166,303 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:6">
+      <c r="G1" s="4"/>
+      <c r="H1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="4"/>
+      <c r="J1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="6"/>
+      <c r="L1" s="7"/>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:12">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" s="2" customFormat="1" spans="1:6">
+      <c r="F2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="4"/>
+      <c r="H2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="4"/>
+      <c r="J2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="6"/>
+      <c r="L2" s="7"/>
+    </row>
+    <row r="3" s="2" customFormat="1" spans="1:12">
       <c r="A3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="L3" s="9"/>
+    </row>
+    <row r="4" s="2" customFormat="1" spans="1:12">
+      <c r="A4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" s="2" customFormat="1" spans="1:12">
+      <c r="A5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="10">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>12</v>
+      </c>
+      <c r="G6">
         <v>10</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="H6">
+        <v>12</v>
+      </c>
+      <c r="I6">
+        <v>10</v>
+      </c>
+      <c r="J6">
         <v>1</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
         <v>11</v>
       </c>
-      <c r="D3" s="2" t="s">
+    </row>
+    <row r="7" spans="1:12">
+      <c r="E7" s="10"/>
+      <c r="H7">
+        <v>13</v>
+      </c>
+      <c r="I7">
+        <v>20</v>
+      </c>
+      <c r="K7">
+        <v>2</v>
+      </c>
+      <c r="L7">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="E8" s="10"/>
+      <c r="K8">
+        <v>3</v>
+      </c>
+      <c r="L8">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="E9" s="10"/>
+      <c r="K9">
+        <v>4</v>
+      </c>
+      <c r="L9">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="E10" s="10"/>
+      <c r="K10">
+        <v>5</v>
+      </c>
+      <c r="L10">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="E11" s="10"/>
+      <c r="J11">
+        <v>2</v>
+      </c>
+      <c r="K11">
         <v>12</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="L11">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="E12" s="10"/>
+      <c r="K12">
+        <v>123</v>
+      </c>
+      <c r="L12">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="E13" s="10"/>
+      <c r="K13">
+        <v>12345</v>
+      </c>
+      <c r="L13">
+        <v>123456</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="B14">
+        <v>2</v>
+      </c>
+      <c r="C14" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" s="10">
+        <v>111</v>
+      </c>
+      <c r="F14">
         <v>13</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G14">
+        <v>10</v>
+      </c>
+      <c r="H14">
+        <v>12</v>
+      </c>
+      <c r="I14">
+        <v>10</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="L14">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="H15">
+        <v>13</v>
+      </c>
+      <c r="I15">
+        <v>100</v>
+      </c>
+      <c r="K15">
+        <v>2</v>
+      </c>
+      <c r="L15">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="H16">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="3">
-        <v>1</v>
-      </c>
-      <c r="F4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="3">
-        <v>111</v>
-      </c>
-      <c r="F5" t="s">
-        <v>20</v>
+      <c r="I16">
+        <v>1000</v>
+      </c>
+      <c r="K16">
+        <v>3</v>
+      </c>
+      <c r="L16">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="J1:L1"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="K3:L3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
@@ -1172,7 +1473,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1184,7 +1485,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/data/test3/testXlsx3.xlsx
+++ b/data/test3/testXlsx3.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="11784" windowHeight="5016"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="28">
   <si>
     <t>##字段名称</t>
   </si>
@@ -50,6 +50,9 @@
   </si>
   <si>
     <t>*item_award</t>
+  </si>
+  <si>
+    <t>*item_test</t>
   </si>
   <si>
     <t>##数据类型</t>
@@ -789,7 +792,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -805,13 +808,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1135,18 +1132,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="15.1083333333333" customWidth="1"/>
-    <col min="3" max="3" width="13.8916666666667" customWidth="1"/>
+    <col min="1" max="1" width="15.1111111111111" customWidth="1"/>
+    <col min="3" max="3" width="13.8888888888889" customWidth="1"/>
     <col min="4" max="4" width="27.6666666666667" customWidth="1"/>
-    <col min="5" max="5" width="19.775" customWidth="1"/>
-    <col min="6" max="6" width="12.625" customWidth="1"/>
-    <col min="7" max="7" width="13.875" customWidth="1"/>
+    <col min="5" max="5" width="19.7777777777778" customWidth="1"/>
+    <col min="6" max="6" width="12.6296296296296" customWidth="1"/>
+    <col min="7" max="7" width="13.8796296296296" customWidth="1"/>
     <col min="8" max="8" width="14.5" customWidth="1"/>
     <col min="9" max="9" width="20.75" customWidth="1"/>
     <col min="10" max="10" width="13.5" customWidth="1"/>
-    <col min="11" max="11" width="14.125" customWidth="1"/>
+    <col min="11" max="11" width="14.1296296296296" customWidth="1"/>
     <col min="12" max="12" width="17.25" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1174,66 +1171,66 @@
         <v>6</v>
       </c>
       <c r="I1" s="4"/>
-      <c r="J1" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" s="6"/>
-      <c r="L1" s="7"/>
+      <c r="J1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" s="5"/>
+      <c r="L1" s="4"/>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:12">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="F2" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2" s="4"/>
       <c r="H2" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I2" s="4"/>
-      <c r="J2" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="6"/>
-      <c r="L2" s="7"/>
+      <c r="J2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" s="5"/>
+      <c r="L2" s="4"/>
     </row>
     <row r="3" s="2" customFormat="1" spans="1:12">
       <c r="A3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K3" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="L3" s="9"/>
+        <v>15</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="L3" s="7"/>
     </row>
     <row r="4" s="2" customFormat="1" spans="1:12">
       <c r="A4" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>1</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>1</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>1</v>
@@ -1242,45 +1239,45 @@
         <v>1</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" s="2" customFormat="1" spans="1:12">
       <c r="A5" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>20</v>
-      </c>
       <c r="I5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K5" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="L5" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -1288,12 +1285,12 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="10">
+        <v>25</v>
+      </c>
+      <c r="E6" s="8">
         <v>1</v>
       </c>
       <c r="F6">
@@ -1319,7 +1316,7 @@
       </c>
     </row>
     <row r="7" spans="1:12">
-      <c r="E7" s="10"/>
+      <c r="E7" s="8"/>
       <c r="H7">
         <v>13</v>
       </c>
@@ -1334,7 +1331,7 @@
       </c>
     </row>
     <row r="8" spans="1:12">
-      <c r="E8" s="10"/>
+      <c r="E8" s="8"/>
       <c r="K8">
         <v>3</v>
       </c>
@@ -1343,7 +1340,7 @@
       </c>
     </row>
     <row r="9" spans="1:12">
-      <c r="E9" s="10"/>
+      <c r="E9" s="8"/>
       <c r="K9">
         <v>4</v>
       </c>
@@ -1352,7 +1349,7 @@
       </c>
     </row>
     <row r="10" spans="1:12">
-      <c r="E10" s="10"/>
+      <c r="E10" s="8"/>
       <c r="K10">
         <v>5</v>
       </c>
@@ -1361,7 +1358,7 @@
       </c>
     </row>
     <row r="11" spans="1:12">
-      <c r="E11" s="10"/>
+      <c r="E11" s="8"/>
       <c r="J11">
         <v>2</v>
       </c>
@@ -1373,7 +1370,7 @@
       </c>
     </row>
     <row r="12" spans="1:12">
-      <c r="E12" s="10"/>
+      <c r="E12" s="8"/>
       <c r="K12">
         <v>123</v>
       </c>
@@ -1382,7 +1379,7 @@
       </c>
     </row>
     <row r="13" spans="1:12">
-      <c r="E13" s="10"/>
+      <c r="E13" s="8"/>
       <c r="K13">
         <v>12345</v>
       </c>
@@ -1395,12 +1392,12 @@
         <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D14" t="s">
-        <v>26</v>
-      </c>
-      <c r="E14" s="10">
+        <v>27</v>
+      </c>
+      <c r="E14" s="8">
         <v>111</v>
       </c>
       <c r="F14">
@@ -1473,7 +1470,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1485,7 +1482,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
